--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10249.43</v>
+        <v>10396.09</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6508.93</v>
+        <v>6585.28</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8599.92</v>
+        <v>8700.799999999999</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>32212.41</v>
+        <v>32590.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9753.360000000001</v>
+        <v>9867.77</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20703.57</v>
+        <v>21053.72</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10571.52</v>
+        <v>10679.03</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6115.89</v>
+        <v>6178.09</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15776.5</v>
+        <v>15924.47</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11892.39</v>
+        <v>12003.94</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13003.42</v>
+        <v>12904.77</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14722.92</v>
+        <v>14611.23</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22348.76</v>
+        <v>22179.22</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10194.49</v>
+        <v>10117.15</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7635.22</v>
+        <v>7577.29</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>53124.9</v>
+        <v>52227.32</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7165.3</v>
+        <v>7063.61</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10756.52</v>
+        <v>10608.72</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8851.23</v>
+        <v>8729.610000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10174.56</v>
+        <v>10111.48</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6594.43</v>
+        <v>6553.54</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17288.05</v>
+        <v>17366.57</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14705.05</v>
+        <v>14771.84</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9943.58</v>
+        <v>9988.74</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7287.65</v>
+        <v>7320.75</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>47421.68</v>
+        <v>48127.8</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5719.33</v>
+        <v>5804.49</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17179.63</v>
+        <v>17435.44</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>57932.17</v>
+        <v>59033.55</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10444.44</v>
+        <v>10679.99</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>33402.17</v>
+        <v>33632.79</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8327.690000000001</v>
+        <v>8385.18</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>19161.82</v>
+        <v>19294.12</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8386.389999999999</v>
+        <v>8444.290000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15232.96</v>
+        <v>15280.06</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11472.23</v>
+        <v>11507.69</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>11105.81</v>
+        <v>11140.15</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7613.9</v>
+        <v>7637.44</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>35795.41</v>
+        <v>35906.08</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6770.76</v>
+        <v>6791.69</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>51556.72</v>
+        <v>51420.35</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>13616.04</v>
+        <v>13580.03</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>11406.98</v>
+        <v>11376.81</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10063.67</v>
+        <v>9929.620000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6593.48</v>
+        <v>6505.66</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6593.48</v>
+        <v>6505.66</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7418.86</v>
+        <v>7273.64</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8675.540000000001</v>
+        <v>8505.719999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10805.3</v>
+        <v>10645.21</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6593.48</v>
+        <v>6495.8</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>153194.57</v>
+        <v>150046.15</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>22291.54</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>15002.31</v>
+        <v>14693.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
@@ -623,7 +623,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2086,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2151,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2216,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2403,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2903,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2968,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3033,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3098,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3163,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3228,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3354,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3419,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3484,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3610,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3675,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3801,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
